--- a/web/files/港岛-筲箕湾-远晴.xlsx
+++ b/web/files/港岛-筲箕湾-远晴.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,6 +122,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
@@ -202,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -267,7 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -935,7 +943,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -945,17 +953,17 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1043,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1045,17 +1053,17 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1231,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1232,10 +1240,10 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>10764000</v>
+        <v>10924000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>20425</v>
+        <v>20729</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1416,10 +1424,10 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>10552000</v>
+        <v>10816000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>20023</v>
+        <v>20524</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1591,7 +1599,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1600,10 +1608,10 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>10446000</v>
+        <v>10709000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>19822</v>
+        <v>20321</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1784,10 +1792,10 @@
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>10343000</v>
+        <v>10603000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>19626</v>
+        <v>20120</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -1922,10 +1930,10 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>8081000</v>
+        <v>8323000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>18749</v>
+        <v>19311</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -1968,10 +1976,10 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>10241000</v>
+        <v>10498000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>19433</v>
+        <v>19920</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2152,10 +2160,10 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>10140000</v>
+        <v>10394000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>19241</v>
+        <v>19723</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2336,10 +2344,10 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>10040000</v>
+        <v>10291000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>19051</v>
+        <v>19528</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2511,7 +2519,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2520,10 +2528,10 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>9940000</v>
+        <v>10189000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>18861</v>
+        <v>19334</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -2704,10 +2712,10 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>9602000</v>
+        <v>10088000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>18220</v>
+        <v>19142</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -2879,7 +2887,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2888,10 +2896,10 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>9602000</v>
+        <v>9988000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>18220</v>
+        <v>18953</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3063,7 +3071,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3072,10 +3080,10 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>9507000</v>
+        <v>9890000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>18040</v>
+        <v>18767</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3247,7 +3255,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3256,10 +3264,10 @@
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>9459000</v>
+        <v>9792000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>17949</v>
+        <v>18581</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -3431,7 +3439,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3440,10 +3448,10 @@
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>9412000</v>
+        <v>9695000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>17860</v>
+        <v>18397</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -3615,7 +3623,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3624,10 +3632,10 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>9366000</v>
+        <v>9599000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>17772</v>
+        <v>18214</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -3808,10 +3816,10 @@
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>9319000</v>
+        <v>9504000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>17683</v>
+        <v>18034</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -3992,10 +4000,10 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>9181000</v>
+        <v>9409000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>17421</v>
+        <v>17854</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -4176,10 +4184,10 @@
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>9135000</v>
+        <v>9315000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>17334</v>
+        <v>17676</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -4351,7 +4359,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4360,10 +4368,10 @@
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>9135000</v>
+        <v>9221000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>17334</v>
+        <v>17497</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -4544,10 +4552,10 @@
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>9045000</v>
+        <v>9129000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>17163</v>
+        <v>17323</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -4728,10 +4736,10 @@
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>8737000</v>
+        <v>9038000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>16579</v>
+        <v>17150</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -4903,7 +4911,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -4912,10 +4920,10 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>8441000</v>
+        <v>8948000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>16017</v>
+        <v>16979</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -5326,7 +5334,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5336,7 +5344,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -5411,12 +5419,12 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>B | 271呎 (1房)
+招标单位
 -
--
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -5442,7 +5450,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 434呎 (1房)
 $782万
@@ -5450,7 +5458,7 @@
 (14年-09月-10日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 271呎 (1房)
 $555万
@@ -5458,7 +5466,7 @@
 (14年-10月-08日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $568万
@@ -5466,12 +5474,12 @@
 (14年-09月-21日)</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
+招标单位
 -
--
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5489,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 434呎 (1房)
 $780万
@@ -5489,7 +5497,7 @@
 (14年-09月-18日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 271呎 (1房)
 $553万
@@ -5497,7 +5505,7 @@
 (14年-09月-07日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $567万
@@ -5505,12 +5513,12 @@
 (14年-09月-02日)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1076万
-$20,425/呎
-(暂停销售)</t>
+$1092万
+$20,729/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5528,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 434呎 (1房)
 $746万
@@ -5528,7 +5536,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 271呎 (1房)
 $542万
@@ -5536,7 +5544,7 @@
 (14年-10月-02日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $556万
@@ -5547,8 +5555,8 @@
       <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1055万
-$20,023/呎
+$1082万
+$20,524/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -5559,7 +5567,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 434呎 (1房)
 $742万
@@ -5567,7 +5575,7 @@
 (14年-12月-09日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 271呎 (1房)
 $537万
@@ -5575,7 +5583,7 @@
 (14年-09月-07日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 275呎 (1房)
 $550万
@@ -5583,12 +5591,12 @@
 (14年-10月-07日)</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1045万
-$19,822/呎
-(暂停销售)</t>
+$1071万
+$20,321/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5609,12 @@
       <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
-$808万
-$18,749/呎
+$832万
+$19,311/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $532万
@@ -5614,7 +5622,7 @@
 (14年-09月-07日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $545万
@@ -5625,8 +5633,8 @@
       <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1034万
-$19,626/呎
+$1060万
+$20,120/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -5637,7 +5645,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $723万
@@ -5645,7 +5653,7 @@
 (14年-12月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $529万
@@ -5653,7 +5661,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $537万
@@ -5664,8 +5672,8 @@
       <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1024万
-$19,433/呎
+$1050万
+$19,920/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -5676,7 +5684,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $716万
@@ -5684,7 +5692,7 @@
 (14年-10月-21日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $524万
@@ -5692,7 +5700,7 @@
 (14年-08月-09日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 275呎 (1房)
 $531万
@@ -5703,8 +5711,8 @@
       <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1014万
-$19,241/呎
+$1039万
+$19,723/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -5715,7 +5723,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $709万
@@ -5723,7 +5731,7 @@
 (14年-10月-02日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $519万
@@ -5731,7 +5739,7 @@
 (14年-09月-03日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $526万
@@ -5742,8 +5750,8 @@
       <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$1004万
-$19,051/呎
+$1029万
+$19,528/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -5754,7 +5762,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $701万
@@ -5762,7 +5770,7 @@
 (14年-10月-26日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $514万
@@ -5770,7 +5778,7 @@
 (14年-08月-31日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $521万
@@ -5778,12 +5786,12 @@
 (14年-08月-25日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$994万
-$18,861/呎
-(暂停销售)</t>
+$1019万
+$19,334/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5801,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $674万
@@ -5801,7 +5809,7 @@
 (14年-08月-26日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $489万
@@ -5809,7 +5817,7 @@
 (14年-08月-24日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $490万
@@ -5820,8 +5828,8 @@
       <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$960万
-$18,220/呎
+$1009万
+$19,142/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -5832,7 +5840,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $674万
@@ -5840,7 +5848,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $489万
@@ -5848,7 +5856,7 @@
 (14年-08月-26日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $490万
@@ -5856,12 +5864,12 @@
 (14年-08月-01日)</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$960万
-$18,220/呎
-(暂停销售)</t>
+$999万
+$18,953/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5879,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $667万
@@ -5879,7 +5887,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $484万
@@ -5887,7 +5895,7 @@
 (14年-08月-24日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 275呎 (1房)
 $486万
@@ -5895,12 +5903,12 @@
 (14年-08月-18日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$951万
-$18,040/呎
-(暂停销售)</t>
+$989万
+$18,767/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5918,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $650万
@@ -5918,7 +5926,7 @@
 (14年-09月-09日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $481万
@@ -5926,7 +5934,7 @@
 (14年-08月-01日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $483万
@@ -5934,12 +5942,12 @@
 (14年-08月-01日)</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$946万
-$17,949/呎
-(暂停销售)</t>
+$979万
+$18,581/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5957,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $661万
@@ -5957,7 +5965,7 @@
 (14年-09月-07日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $479万
@@ -5965,7 +5973,7 @@
 (14年-08月-27日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $481万
@@ -5973,12 +5981,12 @@
 (14年-08月-28日)</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$941万
-$17,860/呎
-(暂停销售)</t>
+$970万
+$18,397/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5996,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $658万
@@ -5996,7 +6004,7 @@
 (14年-08月-27日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $477万
@@ -6004,7 +6012,7 @@
 (14年-08月-01日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $478万
@@ -6012,12 +6020,12 @@
 (14年-08月-01日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$937万
-$17,772/呎
-(暂停销售)</t>
+$960万
+$18,214/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6035,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $654万
@@ -6035,7 +6043,7 @@
 (14年-09月-09日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $474万
@@ -6043,7 +6051,7 @@
 (14年-08月-26日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $476万
@@ -6054,8 +6062,8 @@
       <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$932万
-$17,683/呎
+$950万
+$18,034/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -6066,7 +6074,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $651万
@@ -6074,7 +6082,7 @@
 (14年-08月-18日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $479万
@@ -6082,7 +6090,7 @@
 (14年-08月-28日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $486万
@@ -6093,8 +6101,8 @@
       <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$918万
-$17,421/呎
+$941万
+$17,854/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -6105,7 +6113,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $648万
@@ -6113,7 +6121,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $477万
@@ -6121,7 +6129,7 @@
 (14年-08月-26日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $484万
@@ -6132,8 +6140,8 @@
       <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$914万
-$17,334/呎
+$932万
+$17,676/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -6144,7 +6152,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $648万
@@ -6152,7 +6160,7 @@
 (14年-08月-27日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $489万
@@ -6160,7 +6168,7 @@
 (14年-09月-07日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $496万
@@ -6168,12 +6176,12 @@
 (14年-09月-07日)</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$914万
-$17,334/呎
-(暂停销售)</t>
+$922万
+$17,497/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6191,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $641万
@@ -6191,7 +6199,7 @@
 (14年-08月-02日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $472万
@@ -6199,7 +6207,7 @@
 (14年-08月-27日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $479万
@@ -6210,8 +6218,8 @@
       <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$904万
-$17,163/呎
+$913万
+$17,323/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -6222,7 +6230,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $629万
@@ -6230,7 +6238,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $463万
@@ -6238,7 +6246,7 @@
 (14年-08月-09日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $462万
@@ -6249,8 +6257,8 @@
       <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$874万
-$16,579/呎
+$904万
+$17,150/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -6261,7 +6269,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 431呎 (1房)
 $616万
@@ -6269,7 +6277,7 @@
 (14年-09月-02日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 274呎 (1房)
 $454万
@@ -6277,7 +6285,7 @@
 (14年-09月-01日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 276呎 (1房)
 $435万
@@ -6285,12 +6293,12 @@
 (14年-08月-24日)</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 527呎 (2房)
-$844万
-$16,017/呎
-(暂停销售)</t>
+$895万
+$16,979/呎
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6316,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 253呎 (1房)
 $500万
@@ -6316,7 +6324,7 @@
 (14年-09月-04日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 254呎 (1房)
 $462万
@@ -6324,7 +6332,7 @@
 (14年-08月-01日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 490呎 (2房)
 $812万

--- a/web/files/港岛-筲箕湾-远晴.xlsx
+++ b/web/files/港岛-筲箕湾-远晴.xlsx
@@ -122,7 +122,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -272,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -789,7 +790,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -889,7 +890,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -943,7 +944,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1043,7 +1044,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1089,7 +1090,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1105,7 +1106,7 @@
         <v>5685000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>20598</v>
+        <v>20673</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1231,7 +1232,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1273,7 +1274,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1289,7 +1290,7 @@
         <v>5670000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>20543</v>
+        <v>20618</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1457,7 +1458,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1473,7 +1474,7 @@
         <v>5559000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>20141</v>
+        <v>20215</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1599,7 +1600,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1825,7 +1826,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -1841,7 +1842,7 @@
         <v>5448000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>19739</v>
+        <v>19811</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2010,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2025,7 +2026,7 @@
         <v>5367000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>19446</v>
+        <v>19516</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2377,7 +2378,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2393,7 +2394,7 @@
         <v>5261000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>19062</v>
+        <v>19131</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2519,7 +2520,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -2561,7 +2562,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -2577,7 +2578,7 @@
         <v>5208000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>18870</v>
+        <v>18938</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -2745,7 +2746,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -2761,7 +2762,7 @@
         <v>4904000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>17768</v>
+        <v>17833</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -2887,7 +2888,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -2929,7 +2930,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -2945,7 +2946,7 @@
         <v>4904000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>17768</v>
+        <v>17833</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3071,7 +3072,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -3255,7 +3256,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -3297,7 +3298,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -3313,7 +3314,7 @@
         <v>4831000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>17504</v>
+        <v>17567</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -3439,7 +3440,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -3481,7 +3482,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -3497,7 +3498,7 @@
         <v>4807000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>17417</v>
+        <v>17480</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -3623,7 +3624,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -3665,7 +3666,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -3681,7 +3682,7 @@
         <v>4783000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>17330</v>
+        <v>17393</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -3849,7 +3850,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -3865,7 +3866,7 @@
         <v>4759000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>17243</v>
+        <v>17305</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4033,7 +4034,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -4049,7 +4050,7 @@
         <v>4859000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>17605</v>
+        <v>17669</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -4217,7 +4218,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -4233,7 +4234,7 @@
         <v>4835000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>17518</v>
+        <v>17582</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -4359,7 +4360,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -4401,7 +4402,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -4417,7 +4418,7 @@
         <v>4958000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>17964</v>
+        <v>18029</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -4585,7 +4586,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4602,7 @@
         <v>4787000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>17344</v>
+        <v>17407</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -4769,7 +4770,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -4785,7 +4786,7 @@
         <v>4625000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>16757</v>
+        <v>16818</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -4911,7 +4912,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -4953,7 +4954,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -4969,7 +4970,7 @@
         <v>4354000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>15775</v>
+        <v>15833</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -5137,7 +5138,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -5153,7 +5154,7 @@
         <v>4623000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>18201</v>
+        <v>18273</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -5329,12 +5330,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -5388,7 +5389,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 1283呎 (3房)
+          <t>A | 1282呎 (3房)
 -
 -
 (暂停销售)</t>
@@ -5424,12 +5425,12 @@
           <t>B | 271呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 -
 -
 (暂停销售)</t>
@@ -5468,9 +5469,9 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $568万
-$20,598/呎
+$20,673/呎
 (14年-09月-21日)</t>
         </is>
       </c>
@@ -5479,7 +5480,7 @@
           <t>D | 527呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5507,9 +5508,9 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $567万
-$20,543/呎
+$20,618/呎
 (14年-09月-02日)</t>
         </is>
       </c>
@@ -5518,7 +5519,7 @@
           <t>D | 527呎 (2房)
 $1092万
 $20,729/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5546,9 +5547,9 @@
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $556万
-$20,141/呎
+$20,215/呎
 (14年-10月-02日)</t>
         </is>
       </c>
@@ -5596,7 +5597,7 @@
           <t>D | 527呎 (2房)
 $1071万
 $20,321/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5624,9 +5625,9 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $545万
-$19,739/呎
+$19,811/呎
 (14年-10月-05日)</t>
         </is>
       </c>
@@ -5663,9 +5664,9 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $537万
-$19,446/呎
+$19,516/呎
 (14年-08月-31日)</t>
         </is>
       </c>
@@ -5741,9 +5742,9 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $526万
-$19,062/呎
+$19,131/呎
 (14年-09月-04日)</t>
         </is>
       </c>
@@ -5780,9 +5781,9 @@
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $521万
-$18,870/呎
+$18,938/呎
 (14年-08月-25日)</t>
         </is>
       </c>
@@ -5791,7 +5792,7 @@
           <t>D | 527呎 (2房)
 $1019万
 $19,334/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5819,9 +5820,9 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $490万
-$17,768/呎
+$17,833/呎
 (14年-08月-01日)</t>
         </is>
       </c>
@@ -5858,9 +5859,9 @@
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $490万
-$17,768/呎
+$17,833/呎
 (14年-08月-01日)</t>
         </is>
       </c>
@@ -5869,7 +5870,7 @@
           <t>D | 527呎 (2房)
 $999万
 $18,953/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5909,7 @@
           <t>D | 527呎 (2房)
 $989万
 $18,767/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5936,9 +5937,9 @@
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $483万
-$17,504/呎
+$17,567/呎
 (14年-08月-01日)</t>
         </is>
       </c>
@@ -5947,7 +5948,7 @@
           <t>D | 527呎 (2房)
 $979万
 $18,581/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -5975,9 +5976,9 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $481万
-$17,417/呎
+$17,480/呎
 (14年-08月-28日)</t>
         </is>
       </c>
@@ -5986,7 +5987,7 @@
           <t>D | 527呎 (2房)
 $970万
 $18,397/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6014,9 +6015,9 @@
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $478万
-$17,330/呎
+$17,393/呎
 (14年-08月-01日)</t>
         </is>
       </c>
@@ -6025,7 +6026,7 @@
           <t>D | 527呎 (2房)
 $960万
 $18,214/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6053,9 +6054,9 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $476万
-$17,243/呎
+$17,305/呎
 (14年-08月-18日)</t>
         </is>
       </c>
@@ -6092,9 +6093,9 @@
       </c>
       <c r="D23" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $486万
-$17,605/呎
+$17,669/呎
 (14年-08月-26日)</t>
         </is>
       </c>
@@ -6131,9 +6132,9 @@
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $484万
-$17,518/呎
+$17,582/呎
 (14年-09月-04日)</t>
         </is>
       </c>
@@ -6170,9 +6171,9 @@
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $496万
-$17,964/呎
+$18,029/呎
 (14年-09月-07日)</t>
         </is>
       </c>
@@ -6181,7 +6182,7 @@
           <t>D | 527呎 (2房)
 $922万
 $17,497/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6209,9 +6210,9 @@
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $479万
-$17,344/呎
+$17,407/呎
 (14年-08月-31日)</t>
         </is>
       </c>
@@ -6248,9 +6249,9 @@
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $462万
-$16,757/呎
+$16,818/呎
 (14年-08月-31日)</t>
         </is>
       </c>
@@ -6287,9 +6288,9 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>C | 276呎 (1房)
+          <t>C | 275呎 (1房)
 $435万
-$15,775/呎
+$15,833/呎
 (14年-08月-24日)</t>
         </is>
       </c>
@@ -6298,7 +6299,7 @@
           <t>D | 527呎 (2房)
 $895万
 $16,979/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -6326,9 +6327,9 @@
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>C | 254呎 (1房)
+          <t>C | 253呎 (1房)
 $462万
-$18,201/呎
+$18,273/呎
 (14年-08月-01日)</t>
         </is>
       </c>
